--- a/docs/import/sample-import-with-errors.xlsx
+++ b/docs/import/sample-import-with-errors.xlsx
@@ -70,7 +70,7 @@
     <t>is_active</t>
   </si>
   <si>
-    <t>00GUMQX</t>
+    <t>00WZBTW</t>
   </si>
   <si>
     <t>قطعهٔ واردشده آزمایشی</t>
@@ -106,28 +106,28 @@
     <t>کد عددی</t>
   </si>
   <si>
-    <t>CUR-MUTGUMQX</t>
+    <t>CUR-MUTWZBTW</t>
   </si>
   <si>
     <t>TOMAN</t>
   </si>
   <si>
-    <t>QTY-MUTGUMQX</t>
-  </si>
-  <si>
-    <t>NEG-MUTGUMQX</t>
+    <t>QTY-MUTWZBTW</t>
+  </si>
+  <si>
+    <t>NEG-MUTWZBTW</t>
   </si>
   <si>
     <t>-5</t>
   </si>
   <si>
-    <t>CAT-MUTGUMQX</t>
+    <t>CAT-MUTWZBTW</t>
   </si>
   <si>
     <t>NOPE</t>
   </si>
   <si>
-    <t>FX-MUTGUMQX</t>
+    <t>FX-MUTWZBTW</t>
   </si>
 </sst>
 </file>

--- a/docs/import/sample-import-with-errors.xlsx
+++ b/docs/import/sample-import-with-errors.xlsx
@@ -70,7 +70,7 @@
     <t>is_active</t>
   </si>
   <si>
-    <t>00WZBTW</t>
+    <t>00W1U60</t>
   </si>
   <si>
     <t>قطعهٔ واردشده آزمایشی</t>
@@ -106,28 +106,28 @@
     <t>کد عددی</t>
   </si>
   <si>
-    <t>CUR-MUTWZBTW</t>
+    <t>CUR-MV3W1U60</t>
   </si>
   <si>
     <t>TOMAN</t>
   </si>
   <si>
-    <t>QTY-MUTWZBTW</t>
-  </si>
-  <si>
-    <t>NEG-MUTWZBTW</t>
+    <t>QTY-MV3W1U60</t>
+  </si>
+  <si>
+    <t>NEG-MV3W1U60</t>
   </si>
   <si>
     <t>-5</t>
   </si>
   <si>
-    <t>CAT-MUTWZBTW</t>
+    <t>CAT-MV3W1U60</t>
   </si>
   <si>
     <t>NOPE</t>
   </si>
   <si>
-    <t>FX-MUTWZBTW</t>
+    <t>FX-MV3W1U60</t>
   </si>
 </sst>
 </file>

--- a/docs/import/sample-import-with-errors.xlsx
+++ b/docs/import/sample-import-with-errors.xlsx
@@ -70,7 +70,7 @@
     <t>is_active</t>
   </si>
   <si>
-    <t>00W1U60</t>
+    <t>002NXD3</t>
   </si>
   <si>
     <t>قطعهٔ واردشده آزمایشی</t>
@@ -106,28 +106,28 @@
     <t>کد عددی</t>
   </si>
   <si>
-    <t>CUR-MV3W1U60</t>
+    <t>CUR-MV92NXD3</t>
   </si>
   <si>
     <t>TOMAN</t>
   </si>
   <si>
-    <t>QTY-MV3W1U60</t>
-  </si>
-  <si>
-    <t>NEG-MV3W1U60</t>
+    <t>QTY-MV92NXD3</t>
+  </si>
+  <si>
+    <t>NEG-MV92NXD3</t>
   </si>
   <si>
     <t>-5</t>
   </si>
   <si>
-    <t>CAT-MV3W1U60</t>
+    <t>CAT-MV92NXD3</t>
   </si>
   <si>
     <t>NOPE</t>
   </si>
   <si>
-    <t>FX-MV3W1U60</t>
+    <t>FX-MV92NXD3</t>
   </si>
 </sst>
 </file>

--- a/docs/import/sample-import-with-errors.xlsx
+++ b/docs/import/sample-import-with-errors.xlsx
@@ -70,7 +70,7 @@
     <t>is_active</t>
   </si>
   <si>
-    <t>002NXD3</t>
+    <t>00CJIQT</t>
   </si>
   <si>
     <t>قطعهٔ واردشده آزمایشی</t>
@@ -106,28 +106,28 @@
     <t>کد عددی</t>
   </si>
   <si>
-    <t>CUR-MV92NXD3</t>
+    <t>CUR-MVDCJIQT</t>
   </si>
   <si>
     <t>TOMAN</t>
   </si>
   <si>
-    <t>QTY-MV92NXD3</t>
-  </si>
-  <si>
-    <t>NEG-MV92NXD3</t>
+    <t>QTY-MVDCJIQT</t>
+  </si>
+  <si>
+    <t>NEG-MVDCJIQT</t>
   </si>
   <si>
     <t>-5</t>
   </si>
   <si>
-    <t>CAT-MV92NXD3</t>
+    <t>CAT-MVDCJIQT</t>
   </si>
   <si>
     <t>NOPE</t>
   </si>
   <si>
-    <t>FX-MV92NXD3</t>
+    <t>FX-MVDCJIQT</t>
   </si>
 </sst>
 </file>

--- a/docs/import/sample-import-with-errors.xlsx
+++ b/docs/import/sample-import-with-errors.xlsx
@@ -70,7 +70,7 @@
     <t>is_active</t>
   </si>
   <si>
-    <t>00CJIQT</t>
+    <t>00DTLGD</t>
   </si>
   <si>
     <t>قطعهٔ واردشده آزمایشی</t>
@@ -106,28 +106,28 @@
     <t>کد عددی</t>
   </si>
   <si>
-    <t>CUR-MVDCJIQT</t>
+    <t>CUR-MVDDTLGD</t>
   </si>
   <si>
     <t>TOMAN</t>
   </si>
   <si>
-    <t>QTY-MVDCJIQT</t>
-  </si>
-  <si>
-    <t>NEG-MVDCJIQT</t>
+    <t>QTY-MVDDTLGD</t>
+  </si>
+  <si>
+    <t>NEG-MVDDTLGD</t>
   </si>
   <si>
     <t>-5</t>
   </si>
   <si>
-    <t>CAT-MVDCJIQT</t>
+    <t>CAT-MVDDTLGD</t>
   </si>
   <si>
     <t>NOPE</t>
   </si>
   <si>
-    <t>FX-MVDCJIQT</t>
+    <t>FX-MVDDTLGD</t>
   </si>
 </sst>
 </file>
